--- a/output/pdf_financials_xlsx/EBM.xlsx
+++ b/output/pdf_financials_xlsx/EBM.xlsx
@@ -1051,25 +1051,25 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.139282</v>
+        <v>-0.139282</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>0.5190979999999999</v>
+        <v>-0.5190979999999999</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.260381</v>
+        <v>-0.260381</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.468479</v>
+        <v>-0.468479</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.489624</v>
+        <v>-0.489624</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.861977</v>
+        <v>-0.861977</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.577328</v>
+        <v>-0.577328</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.603593</v>
@@ -1271,25 +1271,25 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.139282</v>
+        <v>-0.139282</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>0.5190979999999999</v>
+        <v>-0.5190979999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.260381</v>
+        <v>-0.260381</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.468479</v>
+        <v>-0.468479</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.489624</v>
+        <v>-0.489624</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.861977</v>
+        <v>-0.861977</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.577328</v>
+        <v>-0.577328</v>
       </c>
       <c r="I20" s="3" t="n">
         <v>-0.603593</v>
@@ -1400,25 +1400,25 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.139282</v>
+        <v>-0.139282</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>0.5190979999999999</v>
+        <v>-0.5190979999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.260381</v>
+        <v>-0.260381</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.468479</v>
+        <v>-0.468479</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.489624</v>
+        <v>-0.489624</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.861977</v>
+        <v>-0.861977</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.577328</v>
+        <v>-0.577328</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>-0.603593</v>
@@ -1604,25 +1604,25 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.139282</v>
+        <v>-0.139282</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>0.5190979999999999</v>
+        <v>-0.5190979999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.260381</v>
+        <v>-0.260381</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.468479</v>
+        <v>-0.468479</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.489624</v>
+        <v>-0.489624</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.861977</v>
+        <v>-0.861977</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.577328</v>
+        <v>-0.577328</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.603593</v>
@@ -1690,25 +1690,25 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.139282</v>
+        <v>-0.139282</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>0.5190979999999999</v>
+        <v>-0.5190979999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.260381</v>
+        <v>-0.260381</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.468479</v>
+        <v>-0.468479</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.489624</v>
+        <v>-0.489624</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.861977</v>
+        <v>-0.861977</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.577328</v>
+        <v>-0.577328</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.603593</v>
@@ -1733,25 +1733,25 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>25.3015046622185</v>
+        <v>-25.3015046622185</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>118.0323470359919</v>
+        <v>-118.0323470359919</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>22.68793191032559</v>
+        <v>-22.68793191032559</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>105.7958872122381</v>
+        <v>-105.7958872122381</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>105.3577922427242</v>
+        <v>-105.3577922427242</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>117.9625328955921</v>
+        <v>-117.9625328955921</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>46.39024574468684</v>
+        <v>-46.39024574468684</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-68.03846088813991</v>
@@ -1776,25 +1776,25 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-0</v>
@@ -1819,25 +1819,25 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
-        <v>25.3015046622185</v>
+        <v>-25.3015046622185</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>118.0323470359919</v>
+        <v>-118.0323470359919</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>22.68793191032559</v>
+        <v>-22.68793191032559</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>105.7958872122381</v>
+        <v>-105.7958872122381</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>105.3577922427242</v>
+        <v>-105.3577922427242</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>117.9625328955921</v>
+        <v>-117.9625328955921</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>46.39024574468684</v>
+        <v>-46.39024574468684</v>
       </c>
       <c r="I32" s="3" t="n">
         <v>-68.03846088813991</v>
@@ -4562,37 +4562,37 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>0.009514</v>
       </c>
     </row>
     <row r="93">
@@ -7620,7 +7620,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -11526,7 +11530,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E67" t="inlineStr">
         <is>
           <t>-</t>
@@ -13028,7 +13036,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr"/>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E87" t="inlineStr">
         <is>
           <t>-</t>
@@ -16492,7 +16504,11 @@
           <t>Reserves 7 9,514</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr"/>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E132" t="inlineStr">
         <is>
           <t>-</t>
@@ -33377,10 +33393,10 @@
         </is>
       </c>
       <c r="J359" s="5" t="n">
-        <v>0.861977</v>
+        <v>-0.861977</v>
       </c>
       <c r="K359" s="5" t="n">
-        <v>0.577328</v>
+        <v>-0.577328</v>
       </c>
       <c r="L359" t="inlineStr">
         <is>
@@ -34408,10 +34424,10 @@
         </is>
       </c>
       <c r="I373" s="5" t="n">
-        <v>0.489624</v>
+        <v>-0.489624</v>
       </c>
       <c r="J373" s="5" t="n">
-        <v>0.861977</v>
+        <v>-0.861977</v>
       </c>
       <c r="K373" t="inlineStr">
         <is>
@@ -35157,10 +35173,10 @@
         </is>
       </c>
       <c r="H383" s="5" t="n">
-        <v>0.468479</v>
+        <v>-0.468479</v>
       </c>
       <c r="I383" s="5" t="n">
-        <v>0.489624</v>
+        <v>-0.489624</v>
       </c>
       <c r="J383" t="inlineStr">
         <is>
@@ -35651,13 +35667,13 @@
         </is>
       </c>
       <c r="F390" s="5" t="n">
-        <v>0.5190979999999999</v>
+        <v>-0.5190979999999999</v>
       </c>
       <c r="G390" s="5" t="n">
-        <v>0.260381</v>
+        <v>-0.260381</v>
       </c>
       <c r="H390" s="5" t="n">
-        <v>0.468479</v>
+        <v>-0.468479</v>
       </c>
       <c r="I390" t="inlineStr">
         <is>
@@ -36800,10 +36816,10 @@
         </is>
       </c>
       <c r="E406" s="5" t="n">
-        <v>0.139282</v>
+        <v>-0.139282</v>
       </c>
       <c r="F406" s="5" t="n">
-        <v>0.5190979999999999</v>
+        <v>-0.5190979999999999</v>
       </c>
       <c r="G406" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/EBM.xlsx
+++ b/output/pdf_financials_xlsx/EBM.xlsx
@@ -826,7 +826,7 @@
         <v>0.8904029999999999</v>
       </c>
       <c r="M10" s="3" t="n">
-        <v>0.283645</v>
+        <v>0.88376</v>
       </c>
     </row>
     <row r="11">
@@ -869,7 +869,7 @@
         <v>-0.436014</v>
       </c>
       <c r="M11" s="3" t="n">
-        <v>0.267348</v>
+        <v>-0.332767</v>
       </c>
     </row>
     <row r="12">
@@ -891,13 +891,13 @@
         <v>0</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.09382500000000001</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.078435</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.016412</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1616,13 +1616,13 @@
         <v>-0.468479</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.489624</v>
+        <v>-0.583449</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.861977</v>
+        <v>-0.940412</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.577328</v>
+        <v>-0.59374</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.603593</v>
@@ -1702,13 +1702,13 @@
         <v>-0.468479</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.489624</v>
+        <v>-0.583449</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.861977</v>
+        <v>-0.940412</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.577328</v>
+        <v>-0.59374</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-0.603593</v>
@@ -1745,13 +1745,13 @@
         <v>-105.7958872122381</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-105.3577922427242</v>
+        <v>-125.5471515412341</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-117.9625328955921</v>
+        <v>-128.6964518605596</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-46.39024574468684</v>
+        <v>-47.70900512091976</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>-68.03846088813991</v>
@@ -1883,28 +1883,28 @@
         <v>1.530227</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.27138</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.82659</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.62535</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.020868</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.039839</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.018448</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.017704</v>
       </c>
     </row>
     <row r="35">
@@ -1973,28 +1973,28 @@
         <v>1.530227</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.27138</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.82659</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.62535</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.020868</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.039839</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.018448</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.017704</v>
       </c>
     </row>
     <row r="37">
@@ -2513,28 +2513,28 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>2.790166</v>
+        <v>1.518786</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>1.632172</v>
+        <v>0.805582</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.7101769999999999</v>
+        <v>0.084827</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.05185</v>
+        <v>0.030982</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.086872</v>
+        <v>0.047033</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.136516</v>
+        <v>0.118068</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.000797</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.018501</v>
+        <v>0.000797</v>
       </c>
     </row>
     <row r="49">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10764,7 +10764,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -11918,7 +11918,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -27700,7 +27700,7 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
@@ -33060,7 +33060,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">

--- a/output/pdf_financials_xlsx/EBM.xlsx
+++ b/output/pdf_financials_xlsx/EBM.xlsx
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.380693</v>
+        <v>0.382197</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0.418985</v>
@@ -673,10 +673,10 @@
         <v>0.279752</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.319608</v>
+        <v>0.322058</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.341102</v>
+        <v>0.344474</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.289042</v>
@@ -691,7 +691,7 @@
         <v>0.422669</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.383323</v>
+        <v>0.438749</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>0.363882</v>
@@ -2009,22 +2009,22 @@
         </is>
       </c>
       <c r="C37" s="3" t="n">
-        <v>0</v>
+        <v>0.001142</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>0</v>
+        <v>0.002171</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0</v>
+        <v>0.009509999999999999</v>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0</v>
+        <v>0.013571</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0</v>
+        <v>0.321624</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0</v>
+        <v>0.07723099999999999</v>
       </c>
       <c r="I37" s="3" t="n">
         <v>0</v>
@@ -2138,10 +2138,8 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0.000306</v>
       </c>
       <c r="C40" s="3" t="n">
         <v>0.013114</v>
@@ -2189,22 +2187,22 @@
         </is>
       </c>
       <c r="C41" s="3" t="n">
-        <v>0.013114</v>
+        <v>0.014256</v>
       </c>
       <c r="D41" s="3" t="n">
-        <v>0.016917</v>
+        <v>0.019088</v>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.027155</v>
+        <v>0.036665</v>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.027792</v>
+        <v>0.041363</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.35569</v>
+        <v>0.677314</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.07825500000000001</v>
+        <v>0.155486</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.006023</v>
@@ -2513,13 +2511,13 @@
         <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.518786</v>
+        <v>1.505215</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.805582</v>
+        <v>0.483958</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.084827</v>
+        <v>0.007596</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>0.030982</v>
@@ -4920,19 +4918,19 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>-0.00172</v>
+        <v>-0.000146</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>-0.003317</v>
+        <v>-0.009412</v>
       </c>
       <c r="D101" s="3" t="n">
-        <v>-0.007335</v>
+        <v>0.002718</v>
       </c>
       <c r="E101" s="3" t="n">
-        <v>0</v>
+        <v>0.00027</v>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0</v>
+        <v>0.005427</v>
       </c>
       <c r="G101" s="3" t="n">
         <v>-0.306121</v>
@@ -5141,13 +5139,13 @@
         <v>1.577699</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>-0.02657</v>
+        <v>-0.016517</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.152103</v>
+        <v>0.152373</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.2124</v>
+        <v>0.217827</v>
       </c>
       <c r="G106" s="3" t="n">
         <v>-0.215401</v>
@@ -22224,7 +22222,11 @@
           <t>GST/HST Receivable</t>
         </is>
       </c>
-      <c r="D208" t="inlineStr"/>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E208" s="5" t="n">
         <v>0.001574</v>
       </c>
@@ -22670,7 +22672,11 @@
           <t>Proceeds from Share Issuance</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr"/>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E214" t="inlineStr">
         <is>
           <t>-</t>
@@ -23272,7 +23278,11 @@
           <t>Proceeds from Share Issuance 5</t>
         </is>
       </c>
-      <c r="D222" t="inlineStr"/>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E222" t="inlineStr">
         <is>
           <t>-</t>
@@ -29270,7 +29280,11 @@
           <t>Office Expenses</t>
         </is>
       </c>
-      <c r="D302" t="inlineStr"/>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E302" s="5" t="n">
         <v>0.001504</v>
       </c>
